--- a/feedback_forms/019_plant_cell_experiment_feedback--feedback_forms.xlsx
+++ b/feedback_forms/019_plant_cell_experiment_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lab_facilitators</t>
+          <t>lab_facilitators_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lab Facilitators</t>
+          <t>Lab Facilitators 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lab_supervisor</t>
+          <t>lab_supervisor_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lab Supervisor</t>
+          <t>Lab Supervisor 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>student_attendance</t>
+          <t>student_attendance_2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Student Attendance</t>
+          <t>Student Attendance 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>student_participation</t>
+          <t>student_participation_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Student Participation</t>
+          <t>Student Participation 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
